--- a/stage1/oldcase_x2/out/stats_x2_vs_variants.xlsx
+++ b/stage1/oldcase_x2/out/stats_x2_vs_variants.xlsx
@@ -1006,16 +1006,16 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D15">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E15">
-        <v>557</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1023,16 +1023,16 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1040,16 +1040,16 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>5296</v>
+        <v>4671</v>
       </c>
       <c r="C17">
-        <v>3059</v>
+        <v>3022</v>
       </c>
       <c r="D17">
-        <v>2310</v>
+        <v>2277</v>
       </c>
       <c r="E17">
-        <v>2753</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1057,16 +1057,16 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>0.232</v>
+        <v>0.205</v>
       </c>
       <c r="C18">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="D18">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
       <c r="E18">
-        <v>0.115</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="19" spans="1:5">
